--- a/workbooks/start-of-demographic-transition.xlsx
+++ b/workbooks/start-of-demographic-transition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\@\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9A49F8-A0A2-48E1-9D8F-238C55F4F72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7011787-ECD5-4490-B243-A45CD6C74705}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
+    <workbookView xWindow="5280" yWindow="1515" windowWidth="23985" windowHeight="21000" activeTab="4" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="5" r:id="rId1"/>
@@ -36,9 +36,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -46,14 +46,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -179,7 +179,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,7 +306,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -317,11 +317,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:srgbClr val="0070C0"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -495,6 +495,8 @@
         <c:axId val="445070144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1914"/>
+          <c:min val="1896"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -534,7 +536,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -546,7 +548,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445072544"/>
@@ -596,7 +598,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -608,7 +610,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445070144"/>
@@ -649,7 +651,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -700,7 +702,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -952,7 +954,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="976156048"/>
@@ -1014,7 +1016,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="976161328"/>
@@ -1055,7 +1057,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1103,7 +1105,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1118,7 +1120,7 @@
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:srgbClr val="0070C0"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -1286,6 +1288,7 @@
         <c:axId val="445036544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="1896"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1325,7 +1328,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1337,7 +1340,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445041344"/>
@@ -1387,7 +1390,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1399,7 +1402,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445036544"/>
@@ -1440,7 +1443,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1707,7 +1710,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="976150768"/>
@@ -1769,7 +1772,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="976153648"/>
@@ -1786,7 +1789,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1794,6 +1796,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1817,7 +1820,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1865,7 +1868,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1876,11 +1879,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:srgbClr val="0070C0"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -2048,6 +2051,7 @@
         <c:axId val="445034144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="1896"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2087,7 +2091,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2099,7 +2103,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445041824"/>
@@ -2149,7 +2153,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2161,7 +2165,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445034144"/>
@@ -2202,7 +2206,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2469,7 +2473,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="976203568"/>
@@ -2531,7 +2535,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="976190128"/>
@@ -2572,7 +2576,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2620,7 +2624,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2631,11 +2635,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:srgbClr val="0070C0"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -2803,6 +2807,7 @@
         <c:axId val="445026464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="1896"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2842,7 +2847,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2854,7 +2859,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445036544"/>
@@ -2904,7 +2909,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2916,7 +2921,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="445026464"/>
@@ -2957,7 +2962,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3224,7 +3229,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="976160368"/>
@@ -3286,7 +3291,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="976159888"/>
@@ -3327,7 +3332,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -8412,114 +8417,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA223DA1-90A1-4FE4-821C-7E7F6AA5A7D6}">
   <dimension ref="A2:B32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="15">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2">
       <c r="A5" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2">
       <c r="B9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2">
       <c r="B26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2">
       <c r="B27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2">
       <c r="B28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2">
       <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2">
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2">
       <c r="B32" t="s">
         <v>27</v>
       </c>
@@ -8532,21 +8537,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14800EA2-8841-4A8E-9FAD-F1492223CF40}">
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="14.62890625" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="20" max="20" width="25.41796875" customWidth="1"/>
-    <col min="21" max="21" width="26.3671875" customWidth="1"/>
-    <col min="22" max="22" width="21.7890625" customWidth="1"/>
+    <col min="20" max="20" width="25.375" customWidth="1"/>
+    <col min="21" max="21" width="26.375" customWidth="1"/>
+    <col min="22" max="22" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.3" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:22" ht="18">
       <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:22" ht="15">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -8572,7 +8577,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -8591,7 +8596,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:22">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -8619,7 +8624,7 @@
         <v>0.39167182024320368</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:22">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -8643,7 +8648,7 @@
         <v>0.78334364048642158</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:22">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -8667,7 +8672,7 @@
         <v>1.1750154607296537</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:22">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -8691,7 +8696,7 @@
         <v>1.5666872809729711</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:22">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -8715,7 +8720,7 @@
         <v>1.9583591012161889</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:22">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -8739,7 +8744,7 @@
         <v>2.3500309214594068</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:22">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -8763,7 +8768,7 @@
         <v>2.7417027417027242</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:22">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -8787,7 +8792,7 @@
         <v>3.1333745619459421</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:22">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -8811,7 +8816,7 @@
         <v>3.52504638218916</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:22">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -8835,7 +8840,7 @@
         <v>3.9167182024324774</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:22">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -8859,7 +8864,7 @@
         <v>4.3083900226757095</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:22">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -8883,7 +8888,7 @@
         <v>4.7000618429189132</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:21">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -8907,7 +8912,7 @@
         <v>5.0917336631622447</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:21">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -8931,7 +8936,7 @@
         <v>5.4834054834054484</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:21">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -8955,7 +8960,7 @@
         <v>5.8750773036486663</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:21">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -8979,7 +8984,7 @@
         <v>6.2667491238918842</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:21">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -9003,7 +9008,7 @@
         <v>6.6584209441352158</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:21">
       <c r="A22" s="4">
         <v>1914</v>
       </c>
@@ -9025,9 +9030,9 @@
         <v>7.0500927643784337</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:21">
       <c r="A23" s="4">
-        <f>A22+1</f>
+        <f t="shared" ref="A23:A29" si="4">A22+1</f>
         <v>1915</v>
       </c>
       <c r="C23" s="6">
@@ -9039,185 +9044,185 @@
         <v>1915</v>
       </c>
       <c r="U23" s="6">
-        <f>U22+STEP</f>
+        <f t="shared" ref="U23:U35" si="5">U22+STEP</f>
         <v>7.5276294340546883</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:21">
       <c r="A24" s="4">
-        <f>A23+1</f>
+        <f t="shared" si="4"/>
         <v>1916</v>
       </c>
       <c r="C24" s="6">
-        <f t="shared" ref="C24:C29" si="4">C23-$D$4</f>
+        <f t="shared" ref="C24:C29" si="6">C23-$D$4</f>
         <v>48.631929824561439</v>
       </c>
       <c r="S24" s="4">
-        <f t="shared" ref="S24:S35" si="5">S23+1</f>
+        <f t="shared" ref="S24:S35" si="7">S23+1</f>
         <v>1916</v>
       </c>
       <c r="U24" s="6">
-        <f>U23+STEP</f>
+        <f t="shared" si="5"/>
         <v>8.005166103730943</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:21">
       <c r="A25" s="4">
-        <f>A24+1</f>
+        <f t="shared" si="4"/>
         <v>1917</v>
       </c>
       <c r="C25" s="6">
+        <f t="shared" si="6"/>
+        <v>48.42526315789479</v>
+      </c>
+      <c r="S25" s="4">
+        <f t="shared" si="7"/>
+        <v>1917</v>
+      </c>
+      <c r="U25" s="6">
+        <f t="shared" si="5"/>
+        <v>8.4827027734071976</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" s="4">
         <f t="shared" si="4"/>
-        <v>48.42526315789479</v>
-      </c>
-      <c r="S25" s="4">
+        <v>1918</v>
+      </c>
+      <c r="C26" s="6">
+        <f t="shared" si="6"/>
+        <v>48.218596491228141</v>
+      </c>
+      <c r="S26" s="4">
+        <f t="shared" si="7"/>
+        <v>1918</v>
+      </c>
+      <c r="U26" s="6">
         <f t="shared" si="5"/>
-        <v>1917</v>
-      </c>
-      <c r="U25" s="6">
-        <f>U24+STEP</f>
-        <v>8.4827027734071976</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="4">
-        <f>A25+1</f>
-        <v>1918</v>
-      </c>
-      <c r="C26" s="6">
+        <v>8.9602394430834522</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" s="4">
         <f t="shared" si="4"/>
-        <v>48.218596491228141</v>
-      </c>
-      <c r="S26" s="4">
+        <v>1919</v>
+      </c>
+      <c r="C27" s="6">
+        <f t="shared" si="6"/>
+        <v>48.011929824561491</v>
+      </c>
+      <c r="S27" s="4">
+        <f t="shared" si="7"/>
+        <v>1919</v>
+      </c>
+      <c r="U27" s="6">
         <f t="shared" si="5"/>
-        <v>1918</v>
-      </c>
-      <c r="U26" s="6">
-        <f>U25+STEP</f>
-        <v>8.9602394430834522</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="4">
-        <f>A26+1</f>
-        <v>1919</v>
-      </c>
-      <c r="C27" s="6">
+        <v>9.4377761127597068</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" s="4">
         <f t="shared" si="4"/>
-        <v>48.011929824561491</v>
-      </c>
-      <c r="S27" s="4">
+        <v>1920</v>
+      </c>
+      <c r="C28" s="6">
+        <f t="shared" si="6"/>
+        <v>47.805263157894842</v>
+      </c>
+      <c r="S28" s="4">
+        <f t="shared" si="7"/>
+        <v>1920</v>
+      </c>
+      <c r="U28" s="6">
         <f t="shared" si="5"/>
-        <v>1919</v>
-      </c>
-      <c r="U27" s="6">
-        <f>U26+STEP</f>
-        <v>9.4377761127597068</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="4">
-        <f>A27+1</f>
-        <v>1920</v>
-      </c>
-      <c r="C28" s="6">
+        <v>9.9153127824359615</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" s="4">
         <f t="shared" si="4"/>
-        <v>47.805263157894842</v>
-      </c>
-      <c r="S28" s="4">
-        <f t="shared" si="5"/>
-        <v>1920</v>
-      </c>
-      <c r="U28" s="6">
-        <f>U27+STEP</f>
-        <v>9.9153127824359615</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="4">
-        <f>A28+1</f>
         <v>1921</v>
       </c>
       <c r="C29" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>47.598596491228193</v>
       </c>
       <c r="S29" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1921</v>
       </c>
       <c r="T29" s="9"/>
       <c r="U29" s="12">
-        <f>U28+STEP</f>
+        <f t="shared" si="5"/>
         <v>10.392849452112216</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:21">
       <c r="S30" s="4">
+        <f t="shared" si="7"/>
+        <v>1922</v>
+      </c>
+      <c r="U30" s="6">
         <f t="shared" si="5"/>
-        <v>1922</v>
-      </c>
-      <c r="U30" s="6">
-        <f>U29+STEP</f>
         <v>10.870386121788471</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:21">
       <c r="S31" s="4">
+        <f t="shared" si="7"/>
+        <v>1923</v>
+      </c>
+      <c r="U31" s="6">
         <f t="shared" si="5"/>
-        <v>1923</v>
-      </c>
-      <c r="U31" s="6">
-        <f>U30+STEP</f>
         <v>11.347922791464725</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:21">
       <c r="S32" s="4">
+        <f t="shared" si="7"/>
+        <v>1924</v>
+      </c>
+      <c r="U32" s="6">
         <f t="shared" si="5"/>
-        <v>1924</v>
-      </c>
-      <c r="U32" s="6">
-        <f>U31+STEP</f>
         <v>11.82545946114098</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:21">
       <c r="S33" s="4">
+        <f t="shared" si="7"/>
+        <v>1925</v>
+      </c>
+      <c r="U33" s="6">
         <f t="shared" si="5"/>
-        <v>1925</v>
-      </c>
-      <c r="U33" s="6">
-        <f>U32+STEP</f>
         <v>12.302996130817235</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:21">
       <c r="S34" s="4">
+        <f t="shared" si="7"/>
+        <v>1926</v>
+      </c>
+      <c r="U34" s="6">
         <f t="shared" si="5"/>
-        <v>1926</v>
-      </c>
-      <c r="U34" s="6">
-        <f>U33+STEP</f>
         <v>12.780532800493489</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:21">
       <c r="S35" s="4">
+        <f t="shared" si="7"/>
+        <v>1927</v>
+      </c>
+      <c r="U35" s="6">
         <f t="shared" si="5"/>
-        <v>1927</v>
-      </c>
-      <c r="U35" s="6">
-        <f>U34+STEP</f>
         <v>13.258069470169744</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:21" ht="15">
       <c r="A39" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:21" ht="15">
       <c r="A41" s="3" t="s">
         <v>0</v>
       </c>
@@ -9225,7 +9230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:21">
       <c r="A42" s="4">
         <v>1896</v>
       </c>
@@ -9233,7 +9238,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:21">
       <c r="A43" s="4">
         <f>A42+1</f>
         <v>1897</v>
@@ -9242,141 +9247,141 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:21">
       <c r="A44" s="4">
-        <f t="shared" ref="A44:A59" si="6">A43+1</f>
+        <f t="shared" ref="A44:A59" si="8">A43+1</f>
         <v>1898</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:21">
       <c r="A45" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1899</v>
       </c>
       <c r="B45" s="5">
         <v>51.3</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:21">
       <c r="A46" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1900</v>
       </c>
       <c r="B46" s="5">
         <v>52.1</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:21">
       <c r="A47" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1901</v>
       </c>
       <c r="B47" s="5">
         <v>51.7</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:21">
       <c r="A48" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1902</v>
       </c>
       <c r="B48" s="5">
         <v>52.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2">
       <c r="A49" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1903</v>
       </c>
       <c r="B49" s="5">
         <v>52.1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2">
       <c r="A50" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1904</v>
       </c>
       <c r="B50" s="5">
         <v>52.4</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2">
       <c r="A51" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1905</v>
       </c>
       <c r="B51" s="5"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2">
       <c r="A52" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1906</v>
       </c>
       <c r="B52" s="5">
         <v>51.3</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2">
       <c r="A53" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1907</v>
       </c>
       <c r="B53" s="5">
         <v>51.3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2">
       <c r="A54" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1908</v>
       </c>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2">
       <c r="A55" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1909</v>
       </c>
       <c r="B55" s="5"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2">
       <c r="A56" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1910</v>
       </c>
       <c r="B56" s="5"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2">
       <c r="A57" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1911</v>
       </c>
       <c r="B57" s="5">
         <v>50.7</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2">
       <c r="A58" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1912</v>
       </c>
       <c r="B58" s="5">
         <v>48.7</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2">
       <c r="A59" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1913</v>
       </c>
       <c r="B59" s="5">
         <v>48.6</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2">
       <c r="A60" s="4">
         <v>1914</v>
       </c>
@@ -9393,21 +9398,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F786236-6DB6-44ED-BB49-A78B092F8D0C}">
   <dimension ref="A1:V49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="14.15625" customWidth="1"/>
-    <col min="4" max="4" width="10.9453125" customWidth="1"/>
-    <col min="20" max="20" width="24.9453125" customWidth="1"/>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="20" max="20" width="25" customWidth="1"/>
     <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="23.26171875" customWidth="1"/>
+    <col min="22" max="22" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.3" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:22" ht="18">
       <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:22" ht="15">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -9433,7 +9438,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -9452,7 +9457,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:22">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -9480,7 +9485,7 @@
         <v>0.47753666967625463</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:22">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -9500,11 +9505,11 @@
         <v>3.2629558541266874</v>
       </c>
       <c r="U6" s="6">
-        <f t="shared" ref="U6:U22" si="2">100 - 100 * C6/$C$4</f>
+        <f t="shared" ref="U6:U21" si="2">100 - 100 * C6/$C$4</f>
         <v>0.95507333935249505</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:22">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -9520,7 +9525,7 @@
         <v>1899</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" ref="T7:T22" si="3">100 - 100 * B7/$B$4</f>
+        <f t="shared" ref="T7:T21" si="3">100 - 100 * B7/$B$4</f>
         <v>1.7274472168905959</v>
       </c>
       <c r="U7" s="6">
@@ -9528,7 +9533,7 @@
         <v>1.4326100090286218</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:22">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -9552,7 +9557,7 @@
         <v>1.9101466787048622</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:22">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -9576,7 +9581,7 @@
         <v>2.3876833483811026</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:22">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -9600,7 +9605,7 @@
         <v>2.8652200180573288</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:22">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -9624,7 +9629,7 @@
         <v>3.3427566877335835</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:22">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -9648,7 +9653,7 @@
         <v>3.8202933574097102</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:22">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -9672,7 +9677,7 @@
         <v>4.2978300270859648</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:22">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -9696,7 +9701,7 @@
         <v>4.7753666967621911</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:22">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -9720,7 +9725,7 @@
         <v>5.2529033664384457</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:22">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -9744,7 +9749,7 @@
         <v>5.7304400361146719</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:21">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -9768,7 +9773,7 @@
         <v>6.2079767057908271</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:21">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -9792,7 +9797,7 @@
         <v>6.6855133754670533</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:21">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -9816,7 +9821,7 @@
         <v>7.1630500451432937</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:21">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -9840,7 +9845,7 @@
         <v>7.6405867148195341</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:21">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -9864,7 +9869,7 @@
         <v>8.1181233844957887</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:21">
       <c r="A22" s="4">
         <f>A21+1</f>
         <v>1914</v>
@@ -9883,7 +9888,7 @@
         <v>8.5956600541720434</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:21">
       <c r="A23" s="4">
         <f>A22+1</f>
         <v>1915</v>
@@ -9900,7 +9905,7 @@
         <v>9.073196723848298</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:21">
       <c r="A24" s="4">
         <f>A23+1</f>
         <v>1916</v>
@@ -9917,7 +9922,7 @@
         <v>9.5507333935245526</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:21">
       <c r="A25" s="4">
         <f>A24+1</f>
         <v>1917</v>
@@ -9934,7 +9939,7 @@
         <v>10.028270063200807</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:21">
       <c r="A26" s="4">
         <f>A25+1</f>
         <v>1918</v>
@@ -9944,12 +9949,12 @@
         <v>45.759270725834085</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:21" ht="15">
       <c r="A28" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:21" ht="15">
       <c r="A31" s="3" t="s">
         <v>0</v>
       </c>
@@ -9957,7 +9962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:21">
       <c r="A32" s="4">
         <v>1896</v>
       </c>
@@ -9965,7 +9970,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2">
       <c r="A33" s="4">
         <f>A32+1</f>
         <v>1897</v>
@@ -9974,14 +9979,14 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2">
       <c r="A34" s="4">
         <f t="shared" ref="A34:A49" si="5">A33+1</f>
         <v>1898</v>
       </c>
       <c r="B34" s="5"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2">
       <c r="A35" s="4">
         <f t="shared" si="5"/>
         <v>1899</v>
@@ -9990,7 +9995,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2">
       <c r="A36" s="4">
         <f t="shared" si="5"/>
         <v>1900</v>
@@ -9999,7 +10004,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2">
       <c r="A37" s="4">
         <f t="shared" si="5"/>
         <v>1901</v>
@@ -10008,7 +10013,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2">
       <c r="A38" s="4">
         <f t="shared" si="5"/>
         <v>1902</v>
@@ -10017,7 +10022,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2">
       <c r="A39" s="4">
         <f t="shared" si="5"/>
         <v>1903</v>
@@ -10026,7 +10031,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2">
       <c r="A40" s="4">
         <f t="shared" si="5"/>
         <v>1904</v>
@@ -10035,14 +10040,14 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2">
       <c r="A41" s="4">
         <f t="shared" si="5"/>
         <v>1905</v>
       </c>
       <c r="B41" s="5"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2">
       <c r="A42" s="4">
         <f t="shared" si="5"/>
         <v>1906</v>
@@ -10051,7 +10056,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2">
       <c r="A43" s="4">
         <f t="shared" si="5"/>
         <v>1907</v>
@@ -10060,28 +10065,28 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2">
       <c r="A44" s="4">
         <f t="shared" si="5"/>
         <v>1908</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2">
       <c r="A45" s="4">
         <f t="shared" si="5"/>
         <v>1909</v>
       </c>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2">
       <c r="A46" s="4">
         <f t="shared" si="5"/>
         <v>1910</v>
       </c>
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2">
       <c r="A47" s="4">
         <f t="shared" si="5"/>
         <v>1911</v>
@@ -10090,7 +10095,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2">
       <c r="A48" s="4">
         <f t="shared" si="5"/>
         <v>1912</v>
@@ -10099,7 +10104,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2">
       <c r="A49" s="4">
         <f t="shared" si="5"/>
         <v>1913</v>
@@ -10117,22 +10122,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D1AEA7-EBD2-458F-AB27-099CC8F05D58}">
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="7.89453125" customWidth="1"/>
-    <col min="2" max="2" width="13.578125" customWidth="1"/>
-    <col min="4" max="4" width="10.3125" customWidth="1"/>
-    <col min="20" max="20" width="24.68359375" customWidth="1"/>
-    <col min="21" max="21" width="18.734375" customWidth="1"/>
-    <col min="22" max="22" width="26.05078125" customWidth="1"/>
+    <col min="1" max="1" width="7.875" customWidth="1"/>
+    <col min="2" max="2" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="20" max="20" width="24.625" customWidth="1"/>
+    <col min="21" max="21" width="18.75" customWidth="1"/>
+    <col min="22" max="22" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.3" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:22" ht="18">
       <c r="A1" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:22" ht="15">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -10158,7 +10163,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -10177,7 +10182,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:22">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -10205,7 +10210,7 @@
         <v>1.0623804165320649</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:22">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -10229,7 +10234,7 @@
         <v>2.1247608330641157</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:22">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -10253,7 +10258,7 @@
         <v>3.1871412495961806</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:22">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -10277,7 +10282,7 @@
         <v>4.2495216661282171</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:22">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -10301,7 +10306,7 @@
         <v>5.3119020826602679</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:22">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -10325,7 +10330,7 @@
         <v>6.3742824991923328</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:22">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -10349,7 +10354,7 @@
         <v>7.4366629157246251</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:22">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -10373,7 +10378,7 @@
         <v>8.4990433322566901</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:22">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -10397,7 +10402,7 @@
         <v>9.5614237487887266</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:22">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -10421,7 +10426,7 @@
         <v>10.623804165320777</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:22">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -10445,7 +10450,7 @@
         <v>11.686184581852842</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:22">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -10469,7 +10474,7 @@
         <v>12.748564998384907</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:21">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -10493,7 +10498,7 @@
         <v>13.810945414916958</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:21">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -10517,7 +10522,7 @@
         <v>14.873325831448994</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:21">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -10541,7 +10546,7 @@
         <v>15.935706247981059</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:21">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -10565,7 +10570,7 @@
         <v>16.998086664513124</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:21">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -10589,7 +10594,7 @@
         <v>18.060467081045175</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:21">
       <c r="A22" s="4">
         <f>A21+1</f>
         <v>1914</v>
@@ -10600,7 +10605,7 @@
         <v>39.187581699346424</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:21">
       <c r="A23" s="4">
         <f>A22+1</f>
         <v>1915</v>
@@ -10610,7 +10615,7 @@
         <v>38.672824217406287</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:21">
       <c r="A24" s="4">
         <f>A23+1</f>
         <v>1916</v>
@@ -10620,7 +10625,7 @@
         <v>38.15806673546615</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:21">
       <c r="A25" s="4">
         <f>A24+1</f>
         <v>1917</v>
@@ -10630,12 +10635,12 @@
         <v>37.643309253526013</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:21" ht="15">
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:21" ht="15">
       <c r="A30" s="3" t="s">
         <v>0</v>
       </c>
@@ -10643,7 +10648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:21">
       <c r="A31" s="4">
         <v>1896</v>
       </c>
@@ -10651,7 +10656,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:21">
       <c r="A32" s="4">
         <f>A31+1</f>
         <v>1897</v>
@@ -10660,14 +10665,14 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2">
       <c r="A33" s="4">
         <f t="shared" ref="A33:A48" si="4">A32+1</f>
         <v>1898</v>
       </c>
       <c r="B33" s="5"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2">
       <c r="A34" s="4">
         <f t="shared" si="4"/>
         <v>1899</v>
@@ -10676,7 +10681,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2">
       <c r="A35" s="4">
         <f t="shared" si="4"/>
         <v>1900</v>
@@ -10685,7 +10690,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2">
       <c r="A36" s="4">
         <f t="shared" si="4"/>
         <v>1901</v>
@@ -10694,7 +10699,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2">
       <c r="A37" s="4">
         <f t="shared" si="4"/>
         <v>1902</v>
@@ -10703,7 +10708,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2">
       <c r="A38" s="4">
         <f t="shared" si="4"/>
         <v>1903</v>
@@ -10712,7 +10717,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2">
       <c r="A39" s="4">
         <f t="shared" si="4"/>
         <v>1904</v>
@@ -10721,14 +10726,14 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2">
       <c r="A40" s="4">
         <f t="shared" si="4"/>
         <v>1905</v>
       </c>
       <c r="B40" s="5"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2">
       <c r="A41" s="4">
         <f t="shared" si="4"/>
         <v>1906</v>
@@ -10737,7 +10742,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2">
       <c r="A42" s="4">
         <f t="shared" si="4"/>
         <v>1907</v>
@@ -10746,28 +10751,28 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2">
       <c r="A43" s="4">
         <f t="shared" si="4"/>
         <v>1908</v>
       </c>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2">
       <c r="A44" s="4">
         <f t="shared" si="4"/>
         <v>1909</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2">
       <c r="A45" s="4">
         <f t="shared" si="4"/>
         <v>1910</v>
       </c>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2">
       <c r="A46" s="4">
         <f t="shared" si="4"/>
         <v>1911</v>
@@ -10776,7 +10781,7 @@
         <v>41.4</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2">
       <c r="A47" s="4">
         <f t="shared" si="4"/>
         <v>1912</v>
@@ -10785,7 +10790,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2">
       <c r="A48" s="4">
         <f t="shared" si="4"/>
         <v>1913</v>
@@ -10803,21 +10808,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BD742E-198F-46A1-9FD2-0E0F39E4257B}">
   <dimension ref="A1:V49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="14.5234375" customWidth="1"/>
-    <col min="4" max="4" width="11.62890625" customWidth="1"/>
-    <col min="20" max="20" width="22.578125" customWidth="1"/>
-    <col min="21" max="21" width="21.26171875" customWidth="1"/>
-    <col min="22" max="22" width="24.7890625" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="20" max="20" width="22.625" customWidth="1"/>
+    <col min="21" max="21" width="21.25" customWidth="1"/>
+    <col min="22" max="22" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.3" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:22" ht="18">
       <c r="A1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:22" ht="15">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -10843,7 +10848,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -10862,7 +10867,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:22">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -10890,7 +10895,7 @@
         <v>0.9186477286707202</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:22">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -10914,7 +10919,7 @@
         <v>1.8372954573416678</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:22">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -10938,7 +10943,7 @@
         <v>2.7559431860126153</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:22">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -10962,7 +10967,7 @@
         <v>3.6745909146833071</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:22">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -10986,7 +10991,7 @@
         <v>4.5932386433542547</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:22">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -11010,7 +11015,7 @@
         <v>5.5118863720249607</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:22">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -11034,7 +11039,7 @@
         <v>6.4305341006959083</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:22">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -11058,7 +11063,7 @@
         <v>7.3491818293666284</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:22">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -11082,7 +11087,7 @@
         <v>8.267829558037576</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:22">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -11106,7 +11111,7 @@
         <v>9.186477286708282</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:22">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -11130,7 +11135,7 @@
         <v>10.10512501537923</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:22">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -11154,7 +11159,7 @@
         <v>11.023772744049936</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:21">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -11178,7 +11183,7 @@
         <v>11.942420472720883</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:21">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -11202,7 +11207,7 @@
         <v>12.861068201391575</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:21">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -11226,7 +11231,7 @@
         <v>13.779715930062522</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:21">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -11250,7 +11255,7 @@
         <v>14.698363658733243</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:21">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -11274,7 +11279,7 @@
         <v>15.61701138740419</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:21">
       <c r="A22" s="4">
         <f>A21+1</f>
         <v>1914</v>
@@ -11285,7 +11290,7 @@
         <v>39.905228758169869</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:21">
       <c r="A23" s="4">
         <f>A22+1</f>
         <v>1915</v>
@@ -11295,7 +11300,7 @@
         <v>39.466013071895304</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:21">
       <c r="A24" s="4">
         <f>A23+1</f>
         <v>1916</v>
@@ -11305,7 +11310,7 @@
         <v>39.026797385620739</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:21">
       <c r="A25" s="4">
         <f>A24+1</f>
         <v>1917</v>
@@ -11315,12 +11320,12 @@
         <v>38.587581699346174</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:21" ht="15">
       <c r="A29" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:21" ht="15">
       <c r="A31" s="3" t="s">
         <v>0</v>
       </c>
@@ -11328,7 +11333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:21">
       <c r="A32" s="4">
         <v>1896</v>
       </c>
@@ -11336,7 +11341,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2">
       <c r="A33" s="4">
         <f>A32+1</f>
         <v>1897</v>
@@ -11345,14 +11350,14 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2">
       <c r="A34" s="4">
         <f t="shared" ref="A34:A49" si="5">A33+1</f>
         <v>1898</v>
       </c>
       <c r="B34" s="5"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2">
       <c r="A35" s="4">
         <f t="shared" si="5"/>
         <v>1899</v>
@@ -11361,7 +11366,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2">
       <c r="A36" s="4">
         <f t="shared" si="5"/>
         <v>1900</v>
@@ -11370,7 +11375,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2">
       <c r="A37" s="4">
         <f t="shared" si="5"/>
         <v>1901</v>
@@ -11379,7 +11384,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2">
       <c r="A38" s="4">
         <f t="shared" si="5"/>
         <v>1902</v>
@@ -11388,7 +11393,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2">
       <c r="A39" s="4">
         <f t="shared" si="5"/>
         <v>1903</v>
@@ -11397,7 +11402,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2">
       <c r="A40" s="4">
         <f t="shared" si="5"/>
         <v>1904</v>
@@ -11406,14 +11411,14 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2">
       <c r="A41" s="4">
         <f t="shared" si="5"/>
         <v>1905</v>
       </c>
       <c r="B41" s="5"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2">
       <c r="A42" s="4">
         <f t="shared" si="5"/>
         <v>1906</v>
@@ -11422,7 +11427,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2">
       <c r="A43" s="4">
         <f t="shared" si="5"/>
         <v>1907</v>
@@ -11431,28 +11436,28 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2">
       <c r="A44" s="4">
         <f t="shared" si="5"/>
         <v>1908</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2">
       <c r="A45" s="4">
         <f t="shared" si="5"/>
         <v>1909</v>
       </c>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2">
       <c r="A46" s="4">
         <f t="shared" si="5"/>
         <v>1910</v>
       </c>
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2">
       <c r="A47" s="4">
         <f t="shared" si="5"/>
         <v>1911</v>
@@ -11461,7 +11466,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2">
       <c r="A48" s="4">
         <f t="shared" si="5"/>
         <v>1912</v>
@@ -11470,7 +11475,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2">
       <c r="A49" s="4">
         <f t="shared" si="5"/>
         <v>1913</v>
